--- a/cinema_da_importare.xlsx
+++ b/cinema_da_importare.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apriti Cinema</t>
+          <t>25hours Hotel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1046,10 +1046,10 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>43.7654</v>
+        <v>43.7712</v>
       </c>
       <c r="H23" t="n">
-        <v>11.2497</v>
+        <v>11.249</v>
       </c>
     </row>
     <row r="24">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Astra</t>
+          <t>Arena Pitti</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1098,10 +1098,10 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>43.7713</v>
+        <v>43.7654</v>
       </c>
       <c r="H25" t="n">
-        <v>11.2715</v>
+        <v>11.2497</v>
       </c>
     </row>
     <row r="26">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cinema Castello Firenze</t>
+          <t>Astra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1119,15 +1119,15 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>43.808</v>
+        <v>43.7713</v>
       </c>
       <c r="H26" t="n">
-        <v>11.22</v>
+        <v>11.2715</v>
       </c>
     </row>
     <row r="27">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cinema Chiardiluna</t>
+          <t>Cinema Castello Firenze</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1150,10 +1150,10 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>43.7697</v>
+        <v>43.808</v>
       </c>
       <c r="H27" t="n">
-        <v>11.2345</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="28">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cinema Marconi</t>
+          <t>Cinema Chiardiluna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1171,15 +1171,15 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>43.7581</v>
+        <v>43.7697</v>
       </c>
       <c r="H28" t="n">
-        <v>11.285</v>
+        <v>11.2345</v>
       </c>
     </row>
     <row r="29">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cinema Odeon</t>
+          <t>Cinema Marconi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,10 +1202,10 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>43.771</v>
+        <v>43.7581</v>
       </c>
       <c r="H29" t="n">
-        <v>11.2525</v>
+        <v>11.285</v>
       </c>
     </row>
     <row r="30">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cinema nel Chiostro</t>
+          <t>Cinema Odeon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1228,10 +1228,10 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>43.7793</v>
+        <v>43.771</v>
       </c>
       <c r="H30" t="n">
-        <v>11.2463</v>
+        <v>11.2525</v>
       </c>
     </row>
     <row r="31">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Cinema nel Chiostro</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1254,10 +1254,10 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>43.7363</v>
+        <v>43.7793</v>
       </c>
       <c r="H31" t="n">
-        <v>11.2227</v>
+        <v>11.2463</v>
       </c>
     </row>
     <row r="32">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fiamma</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1275,15 +1275,15 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>43.7831</v>
+        <v>43.7363</v>
       </c>
       <c r="H32" t="n">
-        <v>11.2715</v>
+        <v>11.2227</v>
       </c>
     </row>
     <row r="33">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flog</t>
+          <t>Fiamma</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1301,15 +1301,15 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>43.793</v>
+        <v>43.7831</v>
       </c>
       <c r="H33" t="n">
-        <v>11.246</v>
+        <v>11.2715</v>
       </c>
     </row>
     <row r="34">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Flora</t>
+          <t>Flog</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1327,15 +1327,15 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>43.7963</v>
+        <v>43.793</v>
       </c>
       <c r="H34" t="n">
-        <v>11.241</v>
+        <v>11.246</v>
       </c>
     </row>
     <row r="35">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Giunti Odeon</t>
+          <t>Flora</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1353,15 +1353,15 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>43.771</v>
+        <v>43.7963</v>
       </c>
       <c r="H35" t="n">
-        <v>11.2525</v>
+        <v>11.241</v>
       </c>
     </row>
     <row r="36">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Il Portico</t>
+          <t>Giunti Odeon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1379,15 +1379,15 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>43.7745</v>
+        <v>43.771</v>
       </c>
       <c r="H36" t="n">
-        <v>11.278</v>
+        <v>11.2525</v>
       </c>
     </row>
     <row r="37">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Principe</t>
+          <t>Il Portico</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1410,10 +1410,10 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>43.7825</v>
+        <v>43.7745</v>
       </c>
       <c r="H37" t="n">
-        <v>11.2628</v>
+        <v>11.278</v>
       </c>
     </row>
     <row r="38">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sala Esse</t>
+          <t>La Compagnia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1436,10 +1436,10 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>43.7688</v>
+        <v>43.7788</v>
       </c>
       <c r="H38" t="n">
-        <v>11.2763</v>
+        <v>11.2591</v>
       </c>
     </row>
     <row r="39">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spazio Alfieri</t>
+          <t>Principe</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1457,15 +1457,15 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>43.7693</v>
+        <v>43.7825</v>
       </c>
       <c r="H39" t="n">
-        <v>11.2668</v>
+        <v>11.2628</v>
       </c>
     </row>
     <row r="40">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Don Otello Puccetti</t>
+          <t>Sala Esse</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Firenzuola</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1488,10 +1488,10 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>44.1188</v>
+        <v>43.7688</v>
       </c>
       <c r="H40" t="n">
-        <v>11.378</v>
+        <v>11.2763</v>
       </c>
     </row>
     <row r="41">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Puccini Fornaci di Barga</t>
+          <t>Spazio Alfieri</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fornaci di Barga</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1514,10 +1514,10 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>44.0456</v>
+        <v>43.7693</v>
       </c>
       <c r="H41" t="n">
-        <v>10.4785</v>
+        <v>11.2668</v>
       </c>
     </row>
     <row r="42">
@@ -1526,24 +1526,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nuovo Lido</t>
+          <t>Don Otello Puccetti</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Forte dei Marmi</t>
+          <t>Firenzuola</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>43.9556</v>
+        <v>44.1188</v>
       </c>
       <c r="H42" t="n">
-        <v>10.1695</v>
+        <v>11.378</v>
       </c>
     </row>
     <row r="43">
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Teatro Pacini</t>
+          <t>Puccini Fornaci di Barga</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fucecchio</t>
+          <t>Fornaci di Barga</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1566,10 +1566,10 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>43.7263</v>
+        <v>44.0456</v>
       </c>
       <c r="H43" t="n">
-        <v>10.8088</v>
+        <v>10.4785</v>
       </c>
     </row>
     <row r="44">
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Teatro Boito</t>
+          <t>Nuovo Lido</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Greve in Chianti</t>
+          <t>Forte dei Marmi</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>43.5831</v>
+        <v>43.9556</v>
       </c>
       <c r="H44" t="n">
-        <v>11.3189</v>
+        <v>10.1695</v>
       </c>
     </row>
     <row r="45">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aurelia Antica</t>
+          <t>Teatro Pacini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>42.7429</v>
+        <v>43.7263</v>
       </c>
       <c r="H45" t="n">
-        <v>11.1068</v>
+        <v>10.8088</v>
       </c>
     </row>
     <row r="46">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Florentia</t>
+          <t>Teatro Boito</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Larderello</t>
+          <t>Greve in Chianti</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1644,10 +1644,10 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>43.2394</v>
+        <v>43.5831</v>
       </c>
       <c r="H46" t="n">
-        <v>10.8875</v>
+        <v>11.3189</v>
       </c>
     </row>
     <row r="47">
@@ -1656,24 +1656,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Arena Estiva Lastra a Signa</t>
+          <t>Aurelia Antica</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lastra a Signa</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>43.7618</v>
+        <v>42.7429</v>
       </c>
       <c r="H47" t="n">
-        <v>11.1077</v>
+        <v>11.1068</v>
       </c>
     </row>
     <row r="48">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Teatro delle Arti</t>
+          <t>Florentia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lastra a Signa</t>
+          <t>Larderello</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1696,10 +1696,10 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>43.769212</v>
+        <v>43.2394</v>
       </c>
       <c r="H48" t="n">
-        <v>11.106375</v>
+        <v>10.8875</v>
       </c>
     </row>
     <row r="49">
@@ -1708,24 +1708,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4 Mori</t>
+          <t>Arena Estiva Lastra a Signa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lastra a Signa</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>43.551</v>
+        <v>43.7618</v>
       </c>
       <c r="H49" t="n">
-        <v>10.305</v>
+        <v>11.1077</v>
       </c>
     </row>
     <row r="50">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Arena Ardenza</t>
+          <t>Teatro delle Arti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lastra a Signa</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1748,10 +1748,10 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>43.527</v>
+        <v>43.769212</v>
       </c>
       <c r="H50" t="n">
-        <v>10.301</v>
+        <v>11.106375</v>
       </c>
     </row>
     <row r="51">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Arena Fabbricotti</t>
+          <t>4 Mori</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1769,15 +1769,15 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>43.554</v>
+        <v>43.551</v>
       </c>
       <c r="H51" t="n">
-        <v>10.308</v>
+        <v>10.305</v>
       </c>
     </row>
     <row r="52">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>La Gran Guardia</t>
+          <t>Arena Ardenza</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1795,15 +1795,15 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>43.5513</v>
+        <v>43.527</v>
       </c>
       <c r="H52" t="n">
-        <v>10.3113</v>
+        <v>10.301</v>
       </c>
     </row>
     <row r="53">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>La Meta</t>
+          <t>Arena Fabbricotti</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1826,10 +1826,10 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>43.5242</v>
+        <v>43.554</v>
       </c>
       <c r="H53" t="n">
-        <v>10.3164</v>
+        <v>10.308</v>
       </c>
     </row>
     <row r="54">
@@ -1838,24 +1838,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Splendor</t>
+          <t>La Gran Guardia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Massa</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>44.0277</v>
+        <v>43.5513</v>
       </c>
       <c r="H54" t="n">
-        <v>10.1055</v>
+        <v>10.3113</v>
       </c>
     </row>
     <row r="55">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Teatro dei Servi</t>
+          <t>La Meta</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Massa</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1878,10 +1878,10 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>44.0397</v>
+        <v>43.5242</v>
       </c>
       <c r="H55" t="n">
-        <v>10.1426</v>
+        <v>10.3164</v>
       </c>
     </row>
     <row r="56">
@@ -1890,24 +1890,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cinema nel Parco Villa Renatico Martini</t>
+          <t>Splendor</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Monsummano Terme</t>
+          <t>Massa</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>43.8692</v>
+        <v>44.0277</v>
       </c>
       <c r="H56" t="n">
-        <v>10.8146</v>
+        <v>10.1055</v>
       </c>
     </row>
     <row r="57">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Scipione Ammirato</t>
+          <t>Teatro dei Servi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Montaione</t>
+          <t>Massa</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1930,10 +1930,10 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>43.5526</v>
+        <v>44.0397</v>
       </c>
       <c r="H57" t="n">
-        <v>10.9146</v>
+        <v>10.1426</v>
       </c>
     </row>
     <row r="58">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Teatro Verdi</t>
+          <t>Cinema nel Parco Villa Renatico Martini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Monte San Savino</t>
+          <t>Monsummano Terme</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1956,10 +1956,10 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>43.329</v>
+        <v>43.8692</v>
       </c>
       <c r="H58" t="n">
-        <v>11.723</v>
+        <v>10.8146</v>
       </c>
     </row>
     <row r="59">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cinema Excelsior Montecatini Terme</t>
+          <t>Scipione Ammirato</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Montecatini Terme</t>
+          <t>Montaione</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>43.8846</v>
+        <v>43.5526</v>
       </c>
       <c r="H59" t="n">
-        <v>10.7734</v>
+        <v>10.9146</v>
       </c>
     </row>
     <row r="60">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Imperiale</t>
+          <t>Teatro Verdi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Montecatini Terme</t>
+          <t>Monte San Savino</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>43.8838</v>
+        <v>43.329</v>
       </c>
       <c r="H60" t="n">
-        <v>10.7725</v>
+        <v>11.723</v>
       </c>
     </row>
     <row r="61">
@@ -2020,24 +2020,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cinema Estivo Montespertoli</t>
+          <t>Cinema Excelsior Montecatini Terme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Montespertoli</t>
+          <t>Montecatini Terme</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>43.6426</v>
+        <v>43.8846</v>
       </c>
       <c r="H61" t="n">
-        <v>11.0733</v>
+        <v>10.7734</v>
       </c>
     </row>
     <row r="62">
@@ -2046,24 +2046,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cine8</t>
+          <t>Imperiale</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Montevarchi</t>
+          <t>Montecatini Terme</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>43.5363</v>
+        <v>43.8838</v>
       </c>
       <c r="H62" t="n">
-        <v>11.5628</v>
+        <v>10.7725</v>
       </c>
     </row>
     <row r="63">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cinema Estivo Cinquale</t>
+          <t>Cinema Estivo Montespertoli</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Montignoso</t>
+          <t>Montespertoli</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2086,10 +2086,10 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>43.979</v>
+        <v>43.6426</v>
       </c>
       <c r="H63" t="n">
-        <v>10.1422</v>
+        <v>11.0733</v>
       </c>
     </row>
     <row r="64">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Comunale</t>
+          <t>Cine8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pietrasanta</t>
+          <t>Montevarchi</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>43.9575</v>
+        <v>43.5363</v>
       </c>
       <c r="H64" t="n">
-        <v>10.2305</v>
+        <v>11.5628</v>
       </c>
     </row>
     <row r="65">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cinema Metropolitan</t>
+          <t>Cinema Estivo Cinquale</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Piombino</t>
+          <t>Montignoso</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2138,10 +2138,10 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>42.924</v>
+        <v>43.979</v>
       </c>
       <c r="H65" t="n">
-        <v>10.531</v>
+        <v>10.1422</v>
       </c>
     </row>
     <row r="66">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Arno</t>
+          <t>Comunale</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Pietrasanta</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2164,10 +2164,10 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>43.7106</v>
+        <v>43.9575</v>
       </c>
       <c r="H66" t="n">
-        <v>10.3865</v>
+        <v>10.2305</v>
       </c>
     </row>
     <row r="67">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Arsenale</t>
+          <t>Cinema Metropolitan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Piombino</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2190,10 +2190,10 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>43.7138</v>
+        <v>42.924</v>
       </c>
       <c r="H67" t="n">
-        <v>10.4035</v>
+        <v>10.531</v>
       </c>
     </row>
     <row r="68">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Caffè Lanteri</t>
+          <t>Arno</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2216,10 +2216,10 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>43.714</v>
+        <v>43.7106</v>
       </c>
       <c r="H68" t="n">
-        <v>10.42</v>
+        <v>10.3865</v>
       </c>
     </row>
     <row r="69">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cinema Estivo Roma</t>
+          <t>Arsenale</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2237,15 +2237,15 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>43.726</v>
+        <v>43.7138</v>
       </c>
       <c r="H69" t="n">
-        <v>10.3976</v>
+        <v>10.4035</v>
       </c>
     </row>
     <row r="70">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Isola Verde</t>
+          <t>Caffè Lanteri</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2263,15 +2263,15 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>43.7102</v>
+        <v>43.714</v>
       </c>
       <c r="H70" t="n">
-        <v>10.4336</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="71">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Multisala Odeon</t>
+          <t>Cinema Estivo Roma</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2289,15 +2289,15 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>43.7188</v>
+        <v>43.726</v>
       </c>
       <c r="H71" t="n">
-        <v>10.4038</v>
+        <v>10.3976</v>
       </c>
     </row>
     <row r="72">
@@ -2306,24 +2306,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cinema Estivo Pistoia</t>
+          <t>Isola Verde</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pistoia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>43.9371</v>
+        <v>43.7102</v>
       </c>
       <c r="H72" t="n">
-        <v>10.9126</v>
+        <v>10.4336</v>
       </c>
     </row>
     <row r="73">
@@ -2332,24 +2332,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lux</t>
+          <t>Multisala Odeon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pistoia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>43.9313</v>
+        <v>43.7188</v>
       </c>
       <c r="H73" t="n">
-        <v>10.9138</v>
+        <v>10.4038</v>
       </c>
     </row>
     <row r="74">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arena Estiva Poggio a Caiano</t>
+          <t>Cinema Estivo Pistoia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poggio a Caiano</t>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2372,10 +2372,10 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>43.8155</v>
+        <v>43.9371</v>
       </c>
       <c r="H74" t="n">
-        <v>11.0583</v>
+        <v>10.9126</v>
       </c>
     </row>
     <row r="75">
@@ -2384,24 +2384,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Accademia</t>
+          <t>Lux</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pontassieve</t>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>43.7744</v>
+        <v>43.9313</v>
       </c>
       <c r="H75" t="n">
-        <v>11.44</v>
+        <v>10.9138</v>
       </c>
     </row>
     <row r="76">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Agorà</t>
+          <t>Arena Estiva Poggio a Caiano</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Poggio a Caiano</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2424,10 +2424,10 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>43.664</v>
+        <v>43.8155</v>
       </c>
       <c r="H76" t="n">
-        <v>10.637</v>
+        <v>11.0583</v>
       </c>
     </row>
     <row r="77">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cinema sotto le stelle Pontedera</t>
+          <t>Accademia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pontassieve</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2450,10 +2450,10 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>43.6614</v>
+        <v>43.7744</v>
       </c>
       <c r="H77" t="n">
-        <v>10.6307</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="78">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nello Santi</t>
+          <t>Agorà</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portoferraio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -2476,10 +2476,10 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>42.8163</v>
+        <v>43.664</v>
       </c>
       <c r="H78" t="n">
-        <v>10.3313</v>
+        <v>10.637</v>
       </c>
     </row>
     <row r="79">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Castello dell'Imperatore</t>
+          <t>Cinema sotto le stelle Pontedera</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prato</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -2502,10 +2502,10 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>43.88</v>
+        <v>43.6614</v>
       </c>
       <c r="H79" t="n">
-        <v>11.094</v>
+        <v>10.6307</v>
       </c>
     </row>
     <row r="80">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Centro Pecci</t>
+          <t>Nello Santi</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prato</t>
+          <t>Portoferraio</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2528,10 +2528,10 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>43.8613</v>
+        <v>42.8163</v>
       </c>
       <c r="H80" t="n">
-        <v>11.1095</v>
+        <v>10.3313</v>
       </c>
     </row>
     <row r="81">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cinema Eden</t>
+          <t>Castello dell'Imperatore</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
         <v>43.88</v>
       </c>
       <c r="H81" t="n">
-        <v>11.096</v>
+        <v>11.094</v>
       </c>
     </row>
     <row r="82">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Terminale</t>
+          <t>Centro Pecci</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2580,10 +2580,10 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>43.8769</v>
+        <v>43.8613</v>
       </c>
       <c r="H82" t="n">
-        <v>11.0955</v>
+        <v>11.1095</v>
       </c>
     </row>
     <row r="83">
@@ -2592,24 +2592,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Misericordia</t>
+          <t>Cinema Eden</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Radda in Chianti</t>
+          <t>Prato</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>43.4876</v>
+        <v>43.88</v>
       </c>
       <c r="H83" t="n">
-        <v>11.3758</v>
+        <v>11.096</v>
       </c>
     </row>
     <row r="84">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cinema Excelsior Reggello</t>
+          <t>Terminale</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Reggello</t>
+          <t>Prato</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2632,10 +2632,10 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>43.687</v>
+        <v>43.8769</v>
       </c>
       <c r="H84" t="n">
-        <v>11.537</v>
+        <v>11.0955</v>
       </c>
     </row>
     <row r="85">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Teatro Reggello</t>
+          <t>Misericordia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reggello</t>
+          <t>Radda in Chianti</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2658,10 +2658,10 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>43.6724</v>
+        <v>43.4876</v>
       </c>
       <c r="H85" t="n">
-        <v>11.5408</v>
+        <v>11.3758</v>
       </c>
     </row>
     <row r="86">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arena Dentro Le Mura</t>
+          <t>Cinema Excelsior Reggello</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Casciano in Val di Pesa</t>
+          <t>Reggello</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2684,10 +2684,10 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>43.6598</v>
+        <v>43.687</v>
       </c>
       <c r="H86" t="n">
-        <v>11.1849</v>
+        <v>11.537</v>
       </c>
     </row>
     <row r="87">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Teatro Bucci</t>
+          <t>Arena Dentro Le Mura</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Giovanni in Valdarno</t>
+          <t>San Casciano in Val di Pesa</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -2710,10 +2710,10 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>43.561</v>
+        <v>43.6598</v>
       </c>
       <c r="H87" t="n">
-        <v>11.531</v>
+        <v>11.1849</v>
       </c>
     </row>
     <row r="88">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cinema Verdi</t>
+          <t>Teatro Bucci</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Vincenzo</t>
+          <t>San Giovanni in Valdarno</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -2736,10 +2736,10 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>43.103</v>
+        <v>43.561</v>
       </c>
       <c r="H88" t="n">
-        <v>10.539</v>
+        <v>11.531</v>
       </c>
     </row>
     <row r="89">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cinema sotto le stelle Sansepolcro</t>
+          <t>Cinema Verdi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sansepolcro</t>
+          <t>San Vincenzo</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2762,10 +2762,10 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>43.5702</v>
+        <v>43.103</v>
       </c>
       <c r="H89" t="n">
-        <v>12.1393</v>
+        <v>10.539</v>
       </c>
     </row>
     <row r="90">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nuova Aurora</t>
+          <t>Cinema sotto le stelle Sansepolcro</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
@@ -2800,24 +2800,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lami</t>
+          <t>Nuova Aurora</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Santa Croce sull'Arno</t>
+          <t>Sansepolcro</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>43.7088</v>
+        <v>43.5726</v>
       </c>
       <c r="H91" t="n">
-        <v>10.7788</v>
+        <v>12.1386</v>
       </c>
     </row>
     <row r="92">
@@ -2826,24 +2826,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cabiria</t>
+          <t>Lami</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scandicci</t>
+          <t>Santa Croce sull'Arno</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>43.754</v>
+        <v>43.7088</v>
       </c>
       <c r="H92" t="n">
-        <v>11.182</v>
+        <v>10.7788</v>
       </c>
     </row>
     <row r="93">
@@ -2852,24 +2852,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cinema Estivo Scarperia e San Piero</t>
+          <t>Cabiria</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scarperia e San Piero</t>
+          <t>Scandicci</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>43.9937</v>
+        <v>43.754</v>
       </c>
       <c r="H93" t="n">
-        <v>11.3533</v>
+        <v>11.182</v>
       </c>
     </row>
     <row r="94">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cinema Garibaldi</t>
+          <t>Cinema Estivo Scarperia e San Piero</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2892,10 +2892,10 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>43.995</v>
+        <v>43.9937</v>
       </c>
       <c r="H94" t="n">
-        <v>11.3557</v>
+        <v>11.3533</v>
       </c>
     </row>
     <row r="95">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Schermo Quinto Martini</t>
+          <t>Cinema Garibaldi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seano</t>
+          <t>Scarperia e San Piero</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -2918,10 +2918,10 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>43.8308</v>
+        <v>43.995</v>
       </c>
       <c r="H95" t="n">
-        <v>11.0211</v>
+        <v>11.3557</v>
       </c>
     </row>
     <row r="96">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Scuderie Granducali</t>
+          <t>Schermo Quinto Martini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seravezza</t>
+          <t>Seano</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2944,10 +2944,10 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>43.994</v>
+        <v>43.8308</v>
       </c>
       <c r="H96" t="n">
-        <v>10.22</v>
+        <v>11.0211</v>
       </c>
     </row>
     <row r="97">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Arena Stadio</t>
+          <t>Scuderie Granducali</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Seravezza</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2970,10 +2970,10 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>43.312</v>
+        <v>43.994</v>
       </c>
       <c r="H97" t="n">
-        <v>11.3175</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="98">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Arena Stadio</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2996,10 +2996,10 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>43.3204</v>
+        <v>43.312</v>
       </c>
       <c r="H98" t="n">
-        <v>11.3285</v>
+        <v>11.3175</v>
       </c>
     </row>
     <row r="99">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pendola</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3022,10 +3022,10 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>43.3138</v>
+        <v>43.3204</v>
       </c>
       <c r="H99" t="n">
-        <v>11.3288</v>
+        <v>11.3285</v>
       </c>
     </row>
     <row r="100">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Italia Soci</t>
+          <t>Pendola</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Soci</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3048,10 +3048,10 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>43.7363</v>
+        <v>43.3138</v>
       </c>
       <c r="H100" t="n">
-        <v>11.8113</v>
+        <v>11.3288</v>
       </c>
     </row>
     <row r="101">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cinema Centrale</t>
+          <t>Italia Soci</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Viareggio</t>
+          <t>Soci</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3074,10 +3074,10 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>43.8676</v>
+        <v>43.7363</v>
       </c>
       <c r="H101" t="n">
-        <v>10.2487</v>
+        <v>11.8113</v>
       </c>
     </row>
     <row r="102">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Goldoni</t>
+          <t>Cinema Centrale</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3095,15 +3095,15 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>43.8682</v>
+        <v>43.8676</v>
       </c>
       <c r="H102" t="n">
-        <v>10.2547</v>
+        <v>10.2487</v>
       </c>
     </row>
     <row r="103">
@@ -3112,24 +3112,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Città di Villafranca</t>
+          <t>Goldoni</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Villafranca in Lunigiana</t>
+          <t>Viareggio</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>44.294</v>
+        <v>43.8682</v>
       </c>
       <c r="H103" t="n">
-        <v>9.949</v>
+        <v>10.2547</v>
       </c>
     </row>
     <row r="104">
@@ -3138,23 +3138,49 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Centrale</t>
+          <t>Città di Villafranca</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Volterra</t>
+          <t>Villafranca in Lunigiana</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
+        <v>44.294</v>
+      </c>
+      <c r="H104" t="n">
+        <v>9.949</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Centrale</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Volterra</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="n">
         <v>43.4019</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H105" t="n">
         <v>10.8615</v>
       </c>
     </row>
